--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="871">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1301,6 +1301,9 @@
 Occurrence Codes
 Value codes
 </t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Supporting information</t>
@@ -10454,7 +10457,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>77</v>
@@ -10472,16 +10475,16 @@
         <v>268</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10518,7 +10521,7 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -10551,10 +10554,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10657,10 +10660,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10765,10 +10768,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10875,10 +10878,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10904,14 +10907,14 @@
         <v>380</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10960,7 +10963,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -10983,10 +10986,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11012,16 +11015,16 @@
         <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11049,10 +11052,10 @@
         <v>256</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11070,7 +11073,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>84</v>
@@ -11093,10 +11096,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11122,14 +11125,14 @@
         <v>159</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11157,10 +11160,10 @@
         <v>256</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11178,7 +11181,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11201,10 +11204,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11307,10 +11310,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11415,10 +11418,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11482,7 +11485,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -11523,10 +11526,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11633,10 +11636,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11659,13 +11662,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11716,7 +11719,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11739,10 +11742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11765,19 +11768,19 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11826,7 +11829,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11849,10 +11852,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11878,16 +11881,16 @@
         <v>159</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11915,10 +11918,10 @@
         <v>256</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11936,7 +11939,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11959,20 +11962,20 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>407</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>408</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>77</v>
@@ -11990,16 +11993,16 @@
         <v>268</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12071,10 +12074,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12177,10 +12180,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12285,10 +12288,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12395,10 +12398,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12424,14 +12427,14 @@
         <v>380</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12480,7 +12483,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>84</v>
@@ -12503,10 +12506,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12532,16 +12535,16 @@
         <v>159</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12551,7 +12554,7 @@
         <v>20</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>20</v>
@@ -12569,10 +12572,10 @@
         <v>256</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12590,7 +12593,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -12613,10 +12616,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12642,14 +12645,14 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12678,7 +12681,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12696,7 +12699,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12714,15 +12717,15 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12825,10 +12828,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12933,10 +12936,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13000,7 +13003,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13041,10 +13044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13151,10 +13154,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13180,10 +13183,10 @@
         <v>211</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13222,17 +13225,17 @@
         <v>20</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13255,13 +13258,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>20</v>
@@ -13286,10 +13289,10 @@
         <v>211</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13340,7 +13343,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13358,15 +13361,15 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13389,19 +13392,19 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13450,7 +13453,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13473,10 +13476,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13502,16 +13505,16 @@
         <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13539,10 +13542,10 @@
         <v>256</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -13560,7 +13563,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13583,13 +13586,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>407</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>408</v>
@@ -13614,16 +13617,16 @@
         <v>268</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13695,10 +13698,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13801,10 +13804,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13909,10 +13912,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14019,10 +14022,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14048,14 +14051,14 @@
         <v>380</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14104,7 +14107,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>84</v>
@@ -14127,10 +14130,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14156,16 +14159,16 @@
         <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14175,7 +14178,7 @@
         <v>20</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>20</v>
@@ -14193,10 +14196,10 @@
         <v>256</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -14214,7 +14217,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>84</v>
@@ -14237,10 +14240,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14266,14 +14269,14 @@
         <v>159</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14301,10 +14304,10 @@
         <v>256</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
@@ -14322,7 +14325,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14345,10 +14348,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14451,10 +14454,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14559,10 +14562,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14626,7 +14629,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14667,10 +14670,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14777,10 +14780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14803,13 +14806,13 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14860,7 +14863,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14883,10 +14886,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14912,16 +14915,16 @@
         <v>390</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -14970,7 +14973,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14988,15 +14991,15 @@
         <v>20</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15022,16 +15025,16 @@
         <v>159</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15059,10 +15062,10 @@
         <v>256</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -15080,7 +15083,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15103,13 +15106,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>407</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>408</v>
@@ -15134,16 +15137,16 @@
         <v>268</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15215,10 +15218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15321,10 +15324,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15429,10 +15432,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15539,10 +15542,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15568,14 +15571,14 @@
         <v>380</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15624,7 +15627,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>84</v>
@@ -15647,10 +15650,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15676,16 +15679,16 @@
         <v>159</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15695,7 +15698,7 @@
         <v>20</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>20</v>
@@ -15713,10 +15716,10 @@
         <v>256</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>20</v>
@@ -15734,7 +15737,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -15757,10 +15760,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15786,14 +15789,14 @@
         <v>159</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15821,10 +15824,10 @@
         <v>256</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>20</v>
@@ -15842,7 +15845,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15865,10 +15868,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15971,10 +15974,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16079,10 +16082,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16146,7 +16149,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>20</v>
@@ -16187,10 +16190,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16297,10 +16300,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16323,13 +16326,13 @@
         <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16380,7 +16383,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16403,10 +16406,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16429,19 +16432,19 @@
         <v>20</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -16478,7 +16481,7 @@
         <v>20</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
@@ -16488,7 +16491,7 @@
         <v>174</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16511,13 +16514,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>20</v>
@@ -16539,19 +16542,19 @@
         <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16600,7 +16603,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16623,10 +16626,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16729,10 +16732,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16837,10 +16840,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16863,19 +16866,19 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -16924,7 +16927,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16942,15 +16945,15 @@
         <v>20</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16976,20 +16979,20 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q129" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="R129" t="s" s="2">
         <v>20</v>
@@ -17013,10 +17016,10 @@
         <v>108</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>20</v>
@@ -17034,7 +17037,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17057,10 +17060,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17086,14 +17089,14 @@
         <v>185</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -17103,7 +17106,7 @@
         <v>20</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>20</v>
@@ -17142,7 +17145,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17165,10 +17168,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17194,14 +17197,14 @@
         <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -17211,7 +17214,7 @@
         <v>20</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>20</v>
@@ -17250,7 +17253,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17259,7 +17262,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>96</v>
@@ -17273,10 +17276,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17302,16 +17305,16 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -17321,7 +17324,7 @@
         <v>20</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>20</v>
@@ -17360,7 +17363,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17369,7 +17372,7 @@
         <v>84</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>96</v>
@@ -17383,10 +17386,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17412,16 +17415,16 @@
         <v>159</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>20</v>
@@ -17449,10 +17452,10 @@
         <v>256</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>20</v>
@@ -17470,7 +17473,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17493,10 +17496,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17522,14 +17525,14 @@
         <v>268</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -17578,7 +17581,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17601,10 +17604,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17707,10 +17710,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17815,10 +17818,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17925,10 +17928,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17954,16 +17957,16 @@
         <v>380</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18012,7 +18015,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>84</v>
@@ -18035,10 +18038,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18061,17 +18064,17 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18120,7 +18123,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -18143,10 +18146,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18172,16 +18175,16 @@
         <v>159</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18209,10 +18212,10 @@
         <v>256</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -18230,7 +18233,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18253,10 +18256,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18282,14 +18285,14 @@
         <v>159</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -18317,10 +18320,10 @@
         <v>256</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -18338,7 +18341,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18361,10 +18364,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18390,14 +18393,14 @@
         <v>268</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -18446,7 +18449,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18469,10 +18472,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18575,10 +18578,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18683,10 +18686,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18793,10 +18796,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18822,14 +18825,14 @@
         <v>380</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -18878,7 +18881,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -18901,10 +18904,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18930,16 +18933,16 @@
         <v>159</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -18967,10 +18970,10 @@
         <v>256</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>20</v>
@@ -18988,7 +18991,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19011,10 +19014,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19040,14 +19043,14 @@
         <v>219</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19096,7 +19099,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19119,10 +19122,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19145,17 +19148,17 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>20</v>
@@ -19183,10 +19186,10 @@
         <v>256</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>20</v>
@@ -19204,7 +19207,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -19227,10 +19230,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19253,17 +19256,17 @@
         <v>20</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>20</v>
@@ -19312,7 +19315,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19335,10 +19338,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19364,16 +19367,16 @@
         <v>268</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -19422,7 +19425,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19445,10 +19448,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19551,10 +19554,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19659,10 +19662,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19769,10 +19772,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19798,14 +19801,14 @@
         <v>380</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19854,7 +19857,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -19877,10 +19880,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19906,16 +19909,16 @@
         <v>390</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -19964,7 +19967,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -19987,10 +19990,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20016,16 +20019,16 @@
         <v>143</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -20074,7 +20077,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20097,10 +20100,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20123,17 +20126,17 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>20</v>
@@ -20182,7 +20185,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -20205,10 +20208,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20234,14 +20237,14 @@
         <v>185</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -20290,7 +20293,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20313,10 +20316,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20342,16 +20345,16 @@
         <v>185</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20400,7 +20403,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20423,10 +20426,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20449,19 +20452,19 @@
         <v>20</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20510,7 +20513,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20533,10 +20536,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20562,14 +20565,14 @@
         <v>268</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20618,7 +20621,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20641,10 +20644,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20747,10 +20750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20855,10 +20858,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20965,10 +20968,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20991,19 +20994,19 @@
         <v>20</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -21052,7 +21055,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>84</v>
@@ -21070,15 +21073,15 @@
         <v>20</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21104,14 +21107,14 @@
         <v>159</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -21140,7 +21143,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>20</v>
@@ -21158,7 +21161,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21176,15 +21179,15 @@
         <v>20</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21207,17 +21210,17 @@
         <v>20</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -21266,7 +21269,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21289,10 +21292,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21315,17 +21318,17 @@
         <v>20</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21374,7 +21377,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21397,10 +21400,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21426,14 +21429,14 @@
         <v>268</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21482,7 +21485,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21505,10 +21508,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21611,10 +21614,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21719,10 +21722,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21829,10 +21832,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21858,14 +21861,14 @@
         <v>380</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -21914,7 +21917,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>84</v>
@@ -21937,10 +21940,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22022,7 +22025,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22045,10 +22048,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22074,14 +22077,14 @@
         <v>380</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22130,7 +22133,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22153,10 +22156,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22182,14 +22185,14 @@
         <v>380</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -22238,7 +22241,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22261,10 +22264,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22290,14 +22293,14 @@
         <v>380</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -22346,7 +22349,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22369,10 +22372,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22398,14 +22401,14 @@
         <v>380</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>20</v>
@@ -22454,7 +22457,7 @@
         <v>20</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22477,10 +22480,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22506,14 +22509,14 @@
         <v>159</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22541,10 +22544,10 @@
         <v>256</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>20</v>
@@ -22562,7 +22565,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22585,10 +22588,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22614,16 +22617,16 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22651,10 +22654,10 @@
         <v>256</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22672,7 +22675,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22695,14 +22698,14 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -22724,16 +22727,16 @@
         <v>159</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22761,10 +22764,10 @@
         <v>256</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>20</v>
@@ -22782,7 +22785,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22805,14 +22808,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22834,10 +22837,10 @@
         <v>159</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22868,7 +22871,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>20</v>
@@ -22886,7 +22889,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22909,10 +22912,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22935,17 +22938,17 @@
         <v>20</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -22994,7 +22997,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23017,10 +23020,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23046,16 +23049,16 @@
         <v>159</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>20</v>
@@ -23083,10 +23086,10 @@
         <v>256</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>20</v>
@@ -23104,7 +23107,7 @@
         <v>20</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23127,10 +23130,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23156,16 +23159,16 @@
         <v>159</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>20</v>
@@ -23193,10 +23196,10 @@
         <v>256</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>20</v>
@@ -23214,7 +23217,7 @@
         <v>20</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23237,10 +23240,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23263,17 +23266,17 @@
         <v>20</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>20</v>
@@ -23322,7 +23325,7 @@
         <v>20</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23345,10 +23348,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23371,17 +23374,17 @@
         <v>20</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23409,10 +23412,10 @@
         <v>256</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>20</v>
@@ -23430,7 +23433,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23453,10 +23456,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23479,17 +23482,17 @@
         <v>20</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>20</v>
@@ -23538,7 +23541,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23561,10 +23564,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23587,17 +23590,17 @@
         <v>20</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23646,7 +23649,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23669,10 +23672,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23695,17 +23698,17 @@
         <v>20</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23754,7 +23757,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23777,10 +23780,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23803,19 +23806,19 @@
         <v>20</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23864,7 +23867,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23887,10 +23890,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23913,17 +23916,17 @@
         <v>20</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -23972,7 +23975,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -23995,10 +23998,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24021,19 +24024,19 @@
         <v>20</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24082,7 +24085,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24105,10 +24108,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24131,17 +24134,17 @@
         <v>20</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24190,7 +24193,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24213,10 +24216,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24242,10 +24245,10 @@
         <v>268</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24296,7 +24299,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24319,10 +24322,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24425,10 +24428,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24533,10 +24536,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24643,10 +24646,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24669,19 +24672,19 @@
         <v>20</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24710,7 +24713,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24728,7 +24731,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>84</v>
@@ -24751,10 +24754,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24780,14 +24783,14 @@
         <v>159</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24816,7 +24819,7 @@
       </c>
       <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>20</v>
@@ -24834,7 +24837,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24857,10 +24860,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24944,7 +24947,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -24967,10 +24970,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24996,14 +24999,14 @@
         <v>268</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25052,7 +25055,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25075,10 +25078,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25181,10 +25184,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25289,10 +25292,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25399,10 +25402,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25428,14 +25431,14 @@
         <v>380</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25484,7 +25487,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>84</v>
@@ -25507,10 +25510,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25592,7 +25595,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25615,10 +25618,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25644,14 +25647,14 @@
         <v>159</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25679,10 +25682,10 @@
         <v>256</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>20</v>
@@ -25700,7 +25703,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25723,10 +25726,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25752,16 +25755,16 @@
         <v>159</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>20</v>
@@ -25789,10 +25792,10 @@
         <v>256</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>20</v>
@@ -25810,7 +25813,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25833,14 +25836,14 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -25862,16 +25865,16 @@
         <v>159</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>20</v>
@@ -25899,10 +25902,10 @@
         <v>256</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>20</v>
@@ -25920,7 +25923,7 @@
         <v>20</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>76</v>
@@ -25943,14 +25946,14 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -25972,10 +25975,10 @@
         <v>159</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -26006,7 +26009,7 @@
       </c>
       <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>20</v>
@@ -26024,7 +26027,7 @@
         <v>20</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>76</v>
@@ -26047,10 +26050,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26076,16 +26079,16 @@
         <v>159</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>20</v>
@@ -26113,10 +26116,10 @@
         <v>256</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>20</v>
@@ -26134,7 +26137,7 @@
         <v>20</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -26157,10 +26160,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26186,16 +26189,16 @@
         <v>159</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26223,10 +26226,10 @@
         <v>256</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26244,7 +26247,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>76</v>
@@ -26267,10 +26270,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26293,17 +26296,17 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26352,7 +26355,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26375,10 +26378,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26401,17 +26404,17 @@
         <v>20</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>20</v>
@@ -26460,7 +26463,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26483,10 +26486,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26509,17 +26512,17 @@
         <v>20</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26568,7 +26571,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26591,10 +26594,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26617,19 +26620,19 @@
         <v>20</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>20</v>
@@ -26678,7 +26681,7 @@
         <v>20</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>76</v>
@@ -26701,10 +26704,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26727,17 +26730,17 @@
         <v>20</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>20</v>
@@ -26786,7 +26789,7 @@
         <v>20</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -26809,10 +26812,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26835,19 +26838,19 @@
         <v>20</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>20</v>
@@ -26896,7 +26899,7 @@
         <v>20</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>76</v>
@@ -26919,10 +26922,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26945,17 +26948,17 @@
         <v>20</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -27004,7 +27007,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>76</v>
@@ -27027,10 +27030,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27056,14 +27059,14 @@
         <v>268</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>20</v>
@@ -27112,7 +27115,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27135,10 +27138,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27241,10 +27244,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27349,10 +27352,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27459,10 +27462,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27488,14 +27491,14 @@
         <v>380</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>20</v>
@@ -27544,7 +27547,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>84</v>
@@ -27567,10 +27570,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27652,7 +27655,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27675,10 +27678,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27704,14 +27707,14 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27739,10 +27742,10 @@
         <v>256</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27760,7 +27763,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27783,10 +27786,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27812,16 +27815,16 @@
         <v>159</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27849,10 +27852,10 @@
         <v>256</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>20</v>
@@ -27870,7 +27873,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27893,10 +27896,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27922,16 +27925,16 @@
         <v>159</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -27959,10 +27962,10 @@
         <v>256</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>20</v>
@@ -27980,7 +27983,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -28003,14 +28006,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -28032,10 +28035,10 @@
         <v>159</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -28066,7 +28069,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>20</v>
@@ -28084,7 +28087,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28107,10 +28110,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28136,16 +28139,16 @@
         <v>159</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28173,10 +28176,10 @@
         <v>256</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>20</v>
@@ -28194,7 +28197,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28217,10 +28220,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28246,16 +28249,16 @@
         <v>159</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28283,10 +28286,10 @@
         <v>256</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>20</v>
@@ -28304,7 +28307,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28327,10 +28330,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28353,17 +28356,17 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28412,7 +28415,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28435,10 +28438,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28461,17 +28464,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28520,7 +28523,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28543,10 +28546,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28569,17 +28572,17 @@
         <v>20</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28628,7 +28631,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28651,10 +28654,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28677,19 +28680,19 @@
         <v>20</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>20</v>
@@ -28738,7 +28741,7 @@
         <v>20</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>76</v>
@@ -28761,10 +28764,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28787,17 +28790,17 @@
         <v>20</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>20</v>
@@ -28846,7 +28849,7 @@
         <v>20</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>76</v>
@@ -28869,10 +28872,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28895,19 +28898,19 @@
         <v>20</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>20</v>
@@ -28956,7 +28959,7 @@
         <v>20</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>76</v>
@@ -28979,10 +28982,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -29005,17 +29008,17 @@
         <v>20</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29064,7 +29067,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -29087,10 +29090,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29113,17 +29116,17 @@
         <v>20</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>20</v>
@@ -29172,7 +29175,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="872">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1782,6 +1782,9 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -17324,7 +17327,7 @@
         <v>20</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>20</v>
@@ -17363,7 +17366,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17386,7 +17389,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>450</v>
@@ -17496,10 +17499,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17525,14 +17528,14 @@
         <v>268</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -17581,7 +17584,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17604,10 +17607,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17710,10 +17713,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17818,10 +17821,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17928,10 +17931,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17957,16 +17960,16 @@
         <v>380</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18015,7 +18018,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>84</v>
@@ -18038,10 +18041,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18064,17 +18067,17 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18123,7 +18126,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -18146,10 +18149,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18175,16 +18178,16 @@
         <v>159</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18212,10 +18215,10 @@
         <v>256</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -18233,7 +18236,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18256,10 +18259,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18285,14 +18288,14 @@
         <v>159</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -18320,10 +18323,10 @@
         <v>256</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -18341,7 +18344,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18364,10 +18367,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18393,14 +18396,14 @@
         <v>268</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -18449,7 +18452,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18472,10 +18475,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18578,10 +18581,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18686,10 +18689,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18796,10 +18799,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18825,14 +18828,14 @@
         <v>380</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -18881,7 +18884,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -18904,10 +18907,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18933,16 +18936,16 @@
         <v>159</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -18970,10 +18973,10 @@
         <v>256</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>20</v>
@@ -18991,7 +18994,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19014,10 +19017,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19043,14 +19046,14 @@
         <v>219</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19099,7 +19102,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19122,10 +19125,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19148,17 +19151,17 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>20</v>
@@ -19186,10 +19189,10 @@
         <v>256</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>20</v>
@@ -19207,7 +19210,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -19230,10 +19233,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19256,17 +19259,17 @@
         <v>20</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>20</v>
@@ -19315,7 +19318,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19338,10 +19341,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19367,16 +19370,16 @@
         <v>268</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -19425,7 +19428,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19448,10 +19451,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19554,10 +19557,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19662,10 +19665,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19772,10 +19775,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19801,14 +19804,14 @@
         <v>380</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19857,7 +19860,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -19880,10 +19883,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19909,16 +19912,16 @@
         <v>390</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -19967,7 +19970,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -19990,10 +19993,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20019,16 +20022,16 @@
         <v>143</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -20077,7 +20080,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20100,10 +20103,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20126,17 +20129,17 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>20</v>
@@ -20185,7 +20188,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -20208,10 +20211,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20237,14 +20240,14 @@
         <v>185</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -20293,7 +20296,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20316,10 +20319,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20345,16 +20348,16 @@
         <v>185</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20403,7 +20406,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20426,10 +20429,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20452,19 +20455,19 @@
         <v>20</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20513,7 +20516,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20536,10 +20539,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20565,14 +20568,14 @@
         <v>268</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20621,7 +20624,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20644,10 +20647,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20750,10 +20753,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20858,10 +20861,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20968,10 +20971,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20994,19 +20997,19 @@
         <v>20</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -21055,7 +21058,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>84</v>
@@ -21073,15 +21076,15 @@
         <v>20</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21107,14 +21110,14 @@
         <v>159</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -21143,7 +21146,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>20</v>
@@ -21161,7 +21164,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21179,15 +21182,15 @@
         <v>20</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21210,17 +21213,17 @@
         <v>20</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -21269,7 +21272,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21292,10 +21295,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21318,17 +21321,17 @@
         <v>20</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21377,7 +21380,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21400,10 +21403,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21429,14 +21432,14 @@
         <v>268</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21485,7 +21488,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21508,10 +21511,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21614,10 +21617,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21722,10 +21725,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21832,10 +21835,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21861,14 +21864,14 @@
         <v>380</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -21917,7 +21920,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>84</v>
@@ -21940,10 +21943,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22025,7 +22028,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22048,10 +22051,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22077,14 +22080,14 @@
         <v>380</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22133,7 +22136,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22156,10 +22159,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22185,14 +22188,14 @@
         <v>380</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -22241,7 +22244,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22264,10 +22267,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22293,14 +22296,14 @@
         <v>380</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -22349,7 +22352,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22372,10 +22375,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22401,14 +22404,14 @@
         <v>380</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>20</v>
@@ -22457,7 +22460,7 @@
         <v>20</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22480,10 +22483,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22509,14 +22512,14 @@
         <v>159</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22544,10 +22547,10 @@
         <v>256</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>20</v>
@@ -22565,7 +22568,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22588,10 +22591,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22617,16 +22620,16 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22654,10 +22657,10 @@
         <v>256</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22675,7 +22678,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22698,14 +22701,14 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -22727,16 +22730,16 @@
         <v>159</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22764,10 +22767,10 @@
         <v>256</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>20</v>
@@ -22785,7 +22788,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22808,14 +22811,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -22837,10 +22840,10 @@
         <v>159</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22871,7 +22874,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>20</v>
@@ -22889,7 +22892,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22912,10 +22915,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22938,17 +22941,17 @@
         <v>20</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -22997,7 +23000,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23020,10 +23023,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23049,16 +23052,16 @@
         <v>159</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>20</v>
@@ -23086,10 +23089,10 @@
         <v>256</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>20</v>
@@ -23107,7 +23110,7 @@
         <v>20</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23130,10 +23133,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23159,16 +23162,16 @@
         <v>159</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>20</v>
@@ -23196,10 +23199,10 @@
         <v>256</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>20</v>
@@ -23217,7 +23220,7 @@
         <v>20</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23240,10 +23243,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23269,14 +23272,14 @@
         <v>441</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>20</v>
@@ -23325,7 +23328,7 @@
         <v>20</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23348,10 +23351,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23374,17 +23377,17 @@
         <v>20</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23412,10 +23415,10 @@
         <v>256</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>20</v>
@@ -23433,7 +23436,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23456,10 +23459,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23482,17 +23485,17 @@
         <v>20</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>20</v>
@@ -23541,7 +23544,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23564,10 +23567,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23590,17 +23593,17 @@
         <v>20</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23649,7 +23652,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23672,10 +23675,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23698,17 +23701,17 @@
         <v>20</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23757,7 +23760,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23780,10 +23783,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23809,16 +23812,16 @@
         <v>525</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23867,7 +23870,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23890,10 +23893,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23916,17 +23919,17 @@
         <v>20</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -23975,7 +23978,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -23998,10 +24001,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24024,19 +24027,19 @@
         <v>20</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24085,7 +24088,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24108,10 +24111,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24134,17 +24137,17 @@
         <v>20</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24193,7 +24196,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24216,10 +24219,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24245,10 +24248,10 @@
         <v>268</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24299,7 +24302,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24322,10 +24325,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24428,10 +24431,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24536,10 +24539,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24646,10 +24649,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24672,19 +24675,19 @@
         <v>20</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24713,7 +24716,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24731,7 +24734,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>84</v>
@@ -24754,10 +24757,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24783,14 +24786,14 @@
         <v>159</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24819,7 +24822,7 @@
       </c>
       <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>20</v>
@@ -24837,7 +24840,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24860,10 +24863,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24947,7 +24950,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -24970,10 +24973,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24999,14 +25002,14 @@
         <v>268</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25055,7 +25058,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25078,10 +25081,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25184,10 +25187,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25292,10 +25295,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25402,10 +25405,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25431,14 +25434,14 @@
         <v>380</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25487,7 +25490,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>84</v>
@@ -25510,10 +25513,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25595,7 +25598,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25618,10 +25621,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25647,14 +25650,14 @@
         <v>159</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25682,10 +25685,10 @@
         <v>256</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>20</v>
@@ -25703,7 +25706,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25726,10 +25729,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25755,16 +25758,16 @@
         <v>159</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>20</v>
@@ -25792,10 +25795,10 @@
         <v>256</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>20</v>
@@ -25813,7 +25816,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25836,14 +25839,14 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -25865,16 +25868,16 @@
         <v>159</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>20</v>
@@ -25902,10 +25905,10 @@
         <v>256</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>20</v>
@@ -25923,7 +25926,7 @@
         <v>20</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>76</v>
@@ -25946,14 +25949,14 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -25975,10 +25978,10 @@
         <v>159</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -26009,7 +26012,7 @@
       </c>
       <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>20</v>
@@ -26027,7 +26030,7 @@
         <v>20</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>76</v>
@@ -26050,10 +26053,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26079,16 +26082,16 @@
         <v>159</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>20</v>
@@ -26116,10 +26119,10 @@
         <v>256</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>20</v>
@@ -26137,7 +26140,7 @@
         <v>20</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -26160,10 +26163,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26189,16 +26192,16 @@
         <v>159</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26226,10 +26229,10 @@
         <v>256</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26247,7 +26250,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>76</v>
@@ -26270,10 +26273,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26296,17 +26299,17 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26355,7 +26358,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26378,10 +26381,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26404,17 +26407,17 @@
         <v>20</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>20</v>
@@ -26463,7 +26466,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26486,10 +26489,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26512,17 +26515,17 @@
         <v>20</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26571,7 +26574,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26594,10 +26597,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26623,16 +26626,16 @@
         <v>525</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>20</v>
@@ -26681,7 +26684,7 @@
         <v>20</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>76</v>
@@ -26704,10 +26707,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26730,17 +26733,17 @@
         <v>20</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>20</v>
@@ -26789,7 +26792,7 @@
         <v>20</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -26812,10 +26815,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26838,19 +26841,19 @@
         <v>20</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>20</v>
@@ -26899,7 +26902,7 @@
         <v>20</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>76</v>
@@ -26922,10 +26925,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26948,17 +26951,17 @@
         <v>20</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -27007,7 +27010,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>76</v>
@@ -27030,10 +27033,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27059,14 +27062,14 @@
         <v>268</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>20</v>
@@ -27115,7 +27118,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27138,10 +27141,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27244,10 +27247,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27352,10 +27355,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27462,10 +27465,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27491,14 +27494,14 @@
         <v>380</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>20</v>
@@ -27547,7 +27550,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>84</v>
@@ -27570,10 +27573,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27655,7 +27658,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27678,10 +27681,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27707,14 +27710,14 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27742,10 +27745,10 @@
         <v>256</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27763,7 +27766,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27786,10 +27789,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27815,16 +27818,16 @@
         <v>159</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27852,10 +27855,10 @@
         <v>256</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>20</v>
@@ -27873,7 +27876,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27896,10 +27899,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27925,16 +27928,16 @@
         <v>159</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -27962,10 +27965,10 @@
         <v>256</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>20</v>
@@ -27983,7 +27986,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -28006,14 +28009,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -28035,10 +28038,10 @@
         <v>159</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -28069,7 +28072,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>20</v>
@@ -28087,7 +28090,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28110,10 +28113,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28139,16 +28142,16 @@
         <v>159</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28176,10 +28179,10 @@
         <v>256</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>20</v>
@@ -28197,7 +28200,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28220,10 +28223,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28249,16 +28252,16 @@
         <v>159</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28286,10 +28289,10 @@
         <v>256</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>20</v>
@@ -28307,7 +28310,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28330,10 +28333,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28356,17 +28359,17 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28415,7 +28418,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28438,10 +28441,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28464,17 +28467,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28523,7 +28526,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28546,10 +28549,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28572,17 +28575,17 @@
         <v>20</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28631,7 +28634,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28654,10 +28657,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28683,16 +28686,16 @@
         <v>525</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>20</v>
@@ -28741,7 +28744,7 @@
         <v>20</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>76</v>
@@ -28764,10 +28767,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28790,17 +28793,17 @@
         <v>20</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>20</v>
@@ -28849,7 +28852,7 @@
         <v>20</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>76</v>
@@ -28872,10 +28875,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28898,19 +28901,19 @@
         <v>20</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>20</v>
@@ -28959,7 +28962,7 @@
         <v>20</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>76</v>
@@ -28982,10 +28985,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -29008,17 +29011,17 @@
         <v>20</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29067,7 +29070,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -29090,10 +29093,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29116,17 +29119,17 @@
         <v>20</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>20</v>
@@ -29175,7 +29178,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
     <t>Claim.provider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
     <t>Claim.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>
@@ -3040,7 +3040,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="116.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestInitial.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
